--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_914_Sweden_Baltic.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_914_Sweden_Baltic.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rc673812a74304d58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R6b472a05a8064c50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R89c3b41d4312406a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R11e4d0e347514eee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9e13d826972e4dd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R3741e2c3a82043ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re6ee0910d47c4850"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R32664929ce914cf9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rf0af79a7e2614bcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R5e69e9fd89de44ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rfa300fa2c27a4fce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R9c6b4e49dcbc4530"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ914CommercialTable" displayName="EEZ914CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ914CommercialTable" displayName="EEZ914CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ914FunctionalTable" displayName="EEZ914FunctionalTable" ref="A1:O16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O16"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ914FunctionalTable" displayName="EEZ914FunctionalTable" ref="A1:E16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E16"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ914ValidationTable" displayName="EEZ914ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ914ValidationTable" displayName="EEZ914ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -4915,7 +4869,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfb8f31a9bdc41b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25a292533db142f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4925,20 +4879,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4946,552 +4890,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>10192.122549402602</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.107984695914306</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1282.285395456629</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>10192.122549402602</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1301.312594176814</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$64,A2,'Species'!$U$2:$U$64))</x:f>
-        <x:v>13263137.434931103</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.107984695914306</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1282.285395456629</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>13069209.893803142</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>193927.54112796113</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0148385053651876</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.014838505365187627</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.5997398398</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>39.810717055349734</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.5997398398</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>39.810717055349734</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$64,A3,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>23.876073069098577</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.6</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>39.810717055349734</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>23.876073069098577</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>9750.528311390799</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.469928730406017</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>295.07249602644384</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>9750.528311390799</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>448.8862085520372</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$64,A4,'Species'!$U$2:$U$64))</x:f>
-        <x:v>4376877.685079513</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.469928730406017</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>295.07249602644384</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2877112.7264185897</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1499764.9586609234</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.5212743125737103</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.5212743125737102</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>231017.2252508414</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.2324578085723727</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>170.78817923900087</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>231017.2252508414</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>185.04941976792324</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$64,A5,'Species'!$U$2:$U$64))</x:f>
-        <x:v>42749603.48906383</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.2324578085723727</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>170.78817923900087</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>39455011.27343734</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>3294592.2156264856</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0835025034663857</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.08350250346638563</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.036196954600000004</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.7499999999999996</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>562.3413251903485</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.036196954600000004</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>562.341325190349</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$64,A6,'Species'!$U$2:$U$64))</x:f>
-        <x:v>20.3550434176189</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.7499999999999996</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>562.3413251903485</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>20.355043417618884</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1.7763568394002505e-14</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>8.726863426204606e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>2122.4188115401003</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.2034856350829823</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>159.76646831185855</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>2122.4188115401003</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>200.72751473557005</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$64,A7,'Species'!$U$2:$U$64))</x:f>
-        <x:v>426027.85326846654</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.2034856350829823</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>159.76646831185855</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>339091.3577984139</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>86936.49547005264</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.2563807465766657</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.25638074657666576</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1609.4658131717001</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.118161809234655</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1312.6888889311383</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1609.4658131717001</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1677.1712821406743</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$64,A8,'Species'!$U$2:$U$64))</x:f>
-        <x:v>2699349.8414387633</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.118161809234655</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1312.6888889311383</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>2112727.89006501</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>586621.9513737531</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.2776609113423036</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.2776609113423037</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>3285.2537956323004</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.5094083608069884</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>323.153125560658</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>3285.2537956323004</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>634.3664906167318</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$64,A9,'Species'!$U$2:$U$64))</x:f>
-        <x:v>2084054.92112056</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.5094083608069884</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>323.153125560658</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1061640.032318593</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1022414.888801967</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.9630523130981041</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.9630523130981041</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>31.7719758261</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.692862199385954</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>493.01734589417447</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>31.7719758261</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>493.8784662910135</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$64,A10,'Species'!$U$2:$U$64))</x:f>
-        <x:v>15691.494692029426</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.692862199385954</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>493.01734589417447</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>15664.135195597693</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>27.359496431732623</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0017466330627318</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0017466330627318536</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R152e6248d3c54b3e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a39f7f01cb54e87"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5501,20 +5086,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5522,876 +5097,307 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>9842.6626217051</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.104441094796373</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1271.8652299074956</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>9842.6626217051</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1298.321905514143</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$64,A2,'Species'!$U$2:$U$64))</x:f>
-        <x:v>12778944.490344996</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.104441094796373</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1271.8652299074956</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>12518540.35825687</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>260404.13208812475</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0208014772198557</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.02080147721985572</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>487.91844079059996</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.9671299839569807</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>927.1072642482593</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>487.91844079059996</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1012.1247083722109</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$64,A3,'Species'!$U$2:$U$64))</x:f>
-        <x:v>493834.30959460983</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.9671299839569807</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>927.1072642482593</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>452352.7308176494</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>41481.578776960436</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.091701842281311</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.09170184228131105</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1242.5542132346</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.0912886714923316</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1233.924738974537</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1242.5542132346</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1775.699773776766</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$64,A4,'Species'!$U$2:$U$64))</x:f>
-        <x:v>2206403.2353460467</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.0912886714923316</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1233.924738974537</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1533218.383227215</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>673184.8521188318</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.4390665149095525</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.43906651490955245</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>318.74067477250003</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.8561543402624068</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>718.0494274787382</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>318.74067477250003</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>861.9691522338176</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$64,A5,'Species'!$U$2:$U$64))</x:f>
-        <x:v>274744.6292160868</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.8561543402624068</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>718.0494274787382</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>228871.55903458034</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>45873.07018150648</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.2004315012970899</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.20043150129708992</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.5997398398</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>39.810717055349734</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.5997398398</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>39.810717055349734</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$64,A6,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>23.876073069098577</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.6</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>39.810717055349734</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>23.876073069098577</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1142.7188703673</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.825061845968211</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>668.4391002652998</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1142.7188703673</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1427.505162329593</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$64,A7,'Species'!$U$2:$U$64))</x:f>
-        <x:v>1631237.0865407619</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.825061845968211</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>668.4391002652998</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>763837.9735644978</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>867399.1129762641</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>2.135579982922938</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>1.1355799829229383</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>2435.4992674874</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.697413039915137</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>498.2106877642221</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>2435.4992674874</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1060.9677210287155</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$64,A8,'Species'!$U$2:$U$64))</x:f>
-        <x:v>2583986.107393213</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.697413039915137</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>498.2106877642221</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1213391.7651041567</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1370594.3422890564</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>2.1295563244336058</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>1.1295563244336058</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>141602.59868320887</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.3790526629801376</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>239.36059898472558</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>141602.59868320887</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>240.07663910257835</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$64,A9,'Species'!$U$2:$U$64))</x:f>
-        <x:v>33995475.98005597</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.3790526629801376</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>239.36059898472558</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>33894082.83860659</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>101393.14144938439</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.00299147027911</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.002991470279110014</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>0.0039374486</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>2.53</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>33.88441561392024</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>0.0039374486</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>33.88441561392024</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$64,A10,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>0.13341814482084838</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>2.53</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>33.88441561392024</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>0.13341814482084838</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>0.036196954600000004</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.7499999999999996</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>562.3413251903485</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>0.036196954600000004</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>562.341325190349</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$64,A11,'Species'!$U$2:$U$64))</x:f>
-        <x:v>20.3550434176189</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.7499999999999996</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>562.3413251903485</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>20.355043417618884</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1.7763568394002505e-14</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>8.726863426204606e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>177.1203752114</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.31</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>204.17379446695296</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>177.1203752114</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>204.17379446695293</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$64,A12,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>36163.33908432197</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.31</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
-        <x:v>36163.33908432197</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>38.2470898955</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.1213498264147432</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>132.23603733111196</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>38.2470898955</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>135.50919623830782</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$64,A13,'Species'!$U$2:$U$64))</x:f>
-        <x:v>5182.8324101935095</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.1213498264147432</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>132.23603733111196</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>5057.643607227733</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>125.18880296577663</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0247523971018584</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.024752397101858444</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>92133.1039552355</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.01</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>102.32929922807536</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>92133.1039552355</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>102.32929922807536</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$64,A14,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>9427915.963446667</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.01</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>102.32929922807536</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
-        <x:v>9427915.963446667</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>79.64428029140001</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.1136627807313046</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>129.91604193249808</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>79.64428029140001</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>130.331556413147</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$64,A15,'Species'!$U$2:$U$64))</x:f>
-        <x:v>10380.163009783093</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.1136627807313046</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>129.91604193249808</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>10347.069658021153</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>33.09335176193963</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0031983308178742</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.003198330817874153</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>8507.974098156197</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.3791816966439705</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>239.43172621527478</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>8507.974098156197</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>255.11060855296193</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$64,A16,'Species'!$U$2:$U$64))</x:f>
-        <x:v>2170474.449733465</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.3791816966439705</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>239.43172621527478</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>2037078.924916384</x:v>
       </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>133395.52481708094</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0654837292681512</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.06548372926815117</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G16">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O16">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e7a1be975264bf2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7604e0a62f92418b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6566,7 +5572,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6665,7 +5671,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>65614786.95071076</x:v>
+        <x:v>58930501.54015318</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6679,7 +5685,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>65614786.950710736</x:v>
+        <x:v>62120902.913858816</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6693,7 +5699,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>1.4901161193847656e-8</x:v>
+        <x:v>-6684285.410557561</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6707,7 +5713,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-7.450580596923828e-9</x:v>
+        <x:v>-3493884.0368519276</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6718,9 +5724,9 @@
         <x:v>EEZ_914</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6732,47 +5738,19 @@
         <x:v>EEZ_914</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_914</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_914</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R198e6cde7e83425d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd17f1c7469184407"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6819,7 +5797,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
